--- a/data/meta_televendas.xlsx
+++ b/data/meta_televendas.xlsx
@@ -1,15 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\christian.roque\Desktop\Total_Day\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2F2A9B9-7DCA-47B5-BD24-C5ABBE62ECF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="Planilha1"/>
+    <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -28,21 +39,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -53,14 +57,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -72,26 +69,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -102,10 +93,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="0E2841"/>
@@ -143,71 +134,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -235,7 +226,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -258,11 +249,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -271,13 +262,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -287,7 +278,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -296,7 +287,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -305,7 +296,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -313,10 +304,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -381,73 +372,33 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="4.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2">
-        <v>1134</v>
-      </c>
-      <c r="C2" s="2">
-        <v>10000</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="2">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2">
-        <v>1762</v>
-      </c>
-      <c r="C3" s="2">
-        <v>10000</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="2">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2">
-        <v>1258</v>
-      </c>
-      <c r="C4" s="2">
-        <v>10000</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="2">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2">
-        <v>998</v>
-      </c>
-      <c r="C5" s="2">
-        <v>10000</v>
-      </c>
-    </row>
+    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/meta_televendas.xlsx
+++ b/data/meta_televendas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\christian.roque\Desktop\Total_Day\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2F2A9B9-7DCA-47B5-BD24-C5ABBE62ECF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{082D187D-4177-4474-8FF9-5376A6EDB674}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="5">
   <si>
     <t>filial</t>
   </si>
@@ -35,11 +35,20 @@
   <si>
     <t>meta</t>
   </si>
+  <si>
+    <t>PI</t>
+  </si>
+  <si>
+    <t>MA</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -69,8 +78,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -376,12 +391,12 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -395,10 +410,424 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="5" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1">
+        <v>546</v>
+      </c>
+      <c r="C2" s="2">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1">
+        <v>546</v>
+      </c>
+      <c r="C3" s="2">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1">
+        <v>1281</v>
+      </c>
+      <c r="C4" s="2">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1">
+        <v>2220</v>
+      </c>
+      <c r="C5" s="2">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="1">
+        <v>2571</v>
+      </c>
+      <c r="C6" s="2">
+        <v>62000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="1">
+        <v>1954</v>
+      </c>
+      <c r="C7" s="2">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="1">
+        <v>1312</v>
+      </c>
+      <c r="C8" s="2">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="1">
+        <v>874</v>
+      </c>
+      <c r="C9" s="2">
+        <v>65010.15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="1">
+        <v>1929</v>
+      </c>
+      <c r="C10" s="2">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="1">
+        <v>977</v>
+      </c>
+      <c r="C11" s="2">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="1">
+        <v>672</v>
+      </c>
+      <c r="C12" s="2">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="1">
+        <v>423</v>
+      </c>
+      <c r="C13" s="2">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="1">
+        <v>1087</v>
+      </c>
+      <c r="C14" s="2">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="1">
+        <v>3179</v>
+      </c>
+      <c r="C15" s="2">
+        <v>40221.019999999997</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="1">
+        <v>3449</v>
+      </c>
+      <c r="C16" s="2">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="1">
+        <v>1953</v>
+      </c>
+      <c r="C17" s="2">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <v>9</v>
+      </c>
+      <c r="B18" s="1">
+        <v>1762</v>
+      </c>
+      <c r="C18" s="2">
+        <v>62000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
+        <v>9</v>
+      </c>
+      <c r="B19" s="1">
+        <v>1778</v>
+      </c>
+      <c r="C19" s="2">
+        <v>55000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <v>9</v>
+      </c>
+      <c r="B20" s="1">
+        <v>2727</v>
+      </c>
+      <c r="C20" s="2">
+        <v>59000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <v>9</v>
+      </c>
+      <c r="B21" s="1">
+        <v>3442</v>
+      </c>
+      <c r="C21" s="2">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <v>9</v>
+      </c>
+      <c r="B22" s="1">
+        <v>2494</v>
+      </c>
+      <c r="C22" s="2">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <v>9</v>
+      </c>
+      <c r="B23" s="1">
+        <v>2661</v>
+      </c>
+      <c r="C23" s="2">
+        <v>62000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <v>9</v>
+      </c>
+      <c r="B24" s="1">
+        <v>3465</v>
+      </c>
+      <c r="C24" s="2">
+        <v>19914</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
+        <v>9</v>
+      </c>
+      <c r="B25" s="1">
+        <v>1133</v>
+      </c>
+      <c r="C25" s="2">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
+        <v>9</v>
+      </c>
+      <c r="B26" s="1">
+        <v>3467</v>
+      </c>
+      <c r="C26" s="2">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
+        <v>3</v>
+      </c>
+      <c r="B27" s="1">
+        <v>2845</v>
+      </c>
+      <c r="C27" s="2">
+        <v>21557.751132002279</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
+        <v>3</v>
+      </c>
+      <c r="B28" s="1">
+        <v>691</v>
+      </c>
+      <c r="C28" s="2">
+        <v>69463.864758674012</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
+        <v>3</v>
+      </c>
+      <c r="B29" s="1">
+        <v>1533</v>
+      </c>
+      <c r="C29" s="2">
+        <v>88626.310209342701</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="1">
+        <v>3</v>
+      </c>
+      <c r="B30" s="1">
+        <v>738</v>
+      </c>
+      <c r="C30" s="2">
+        <v>45814.113626671729</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="1">
+        <v>3</v>
+      </c>
+      <c r="B31" s="1">
+        <v>213</v>
+      </c>
+      <c r="C31" s="2">
+        <v>79045.087484008356</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="1">
+        <v>3</v>
+      </c>
+      <c r="B32" s="1">
+        <v>3009</v>
+      </c>
+      <c r="C32" s="2">
+        <v>50301.419308005316</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="1">
+        <v>1</v>
+      </c>
+      <c r="B33" s="1">
+        <v>27</v>
+      </c>
+      <c r="C33" s="2">
+        <v>79006.584099724496</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
+        <v>1</v>
+      </c>
+      <c r="B34" s="1">
+        <v>1139</v>
+      </c>
+      <c r="C34" s="2">
+        <v>81475.539852840913</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="1">
+        <v>1</v>
+      </c>
+      <c r="B35" s="1">
+        <v>675</v>
+      </c>
+      <c r="C35" s="2">
+        <v>69989</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="1">
+        <v>1</v>
+      </c>
+      <c r="B36" s="1">
+        <v>58</v>
+      </c>
+      <c r="C36" s="2">
+        <v>56785.982321676995</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
+        <v>1</v>
+      </c>
+      <c r="B37" s="1">
+        <v>841</v>
+      </c>
+      <c r="C37" s="2">
+        <v>29627.469037396699</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="1">
+        <v>1</v>
+      </c>
+      <c r="B38" s="1">
+        <v>13148</v>
+      </c>
+      <c r="C38" s="2">
+        <v>39503.292049862255</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" s="1">
+        <v>1</v>
+      </c>
+      <c r="B39" s="1">
+        <v>3403</v>
+      </c>
+      <c r="C39" s="2">
+        <v>66661.805334142555</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/meta_televendas.xlsx
+++ b/data/meta_televendas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\christian.roque\Desktop\Total_Day\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{082D187D-4177-4474-8FF9-5376A6EDB674}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33B471A8-D049-4135-A889-92D4B75875D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,16 +46,23 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -75,10 +82,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -86,9 +94,16 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{FB098738-3403-4C67-B238-0CFE129E26F1}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -391,7 +406,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C39"/>
+  <dimension ref="A1:C48"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.44140625" bestFit="1" customWidth="1"/>
@@ -828,6 +843,105 @@
         <v>66661.805334142555</v>
       </c>
     </row>
+    <row r="40" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A40" s="1">
+        <v>7</v>
+      </c>
+      <c r="B40" s="3">
+        <v>519</v>
+      </c>
+      <c r="C40" s="4">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A41" s="1">
+        <v>7</v>
+      </c>
+      <c r="B41" s="3">
+        <v>1883</v>
+      </c>
+      <c r="C41" s="4">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A42" s="1">
+        <v>7</v>
+      </c>
+      <c r="B42" s="3">
+        <v>1885</v>
+      </c>
+      <c r="C42" s="4">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A43" s="1">
+        <v>7</v>
+      </c>
+      <c r="B43" s="3">
+        <v>1899</v>
+      </c>
+      <c r="C43" s="4">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A44" s="1">
+        <v>7</v>
+      </c>
+      <c r="B44" s="3">
+        <v>2184</v>
+      </c>
+      <c r="C44" s="4">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A45" s="1">
+        <v>7</v>
+      </c>
+      <c r="B45" s="3">
+        <v>1884</v>
+      </c>
+      <c r="C45" s="4">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A46" s="1">
+        <v>7</v>
+      </c>
+      <c r="B46" s="3">
+        <v>2185</v>
+      </c>
+      <c r="C46" s="4">
+        <v>33333</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A47" s="1">
+        <v>7</v>
+      </c>
+      <c r="B47" s="3">
+        <v>3389</v>
+      </c>
+      <c r="C47" s="4">
+        <v>33333</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A48" s="1">
+        <v>7</v>
+      </c>
+      <c r="B48" s="3">
+        <v>2985</v>
+      </c>
+      <c r="C48" s="4">
+        <v>33334</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
